--- a/BVSimulationFiles/79.xlsx
+++ b/BVSimulationFiles/79.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004450261780104711</v>
+        <v>0.008900523560209423</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004466745712362157</v>
+        <v>0.008933491424724315</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004483172555714586</v>
+        <v>0.008966345111429172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004499542440959323</v>
+        <v>0.008999084881918647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004515855498634556</v>
+        <v>0.009031710997269113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004532111859019811</v>
+        <v>0.009064223718039622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004548311652136438</v>
+        <v>0.009096623304272876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004564455007748076</v>
+        <v>0.009128910015496152</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004580542055361132</v>
+        <v>0.009161084110722265</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00459657292422525</v>
+        <v>0.009193145848450501</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004612547743333789</v>
+        <v>0.009225095486667579</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004628466641424292</v>
+        <v>0.009256933282848583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004644329746978948</v>
+        <v>0.009288659493957897</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004660137188225074</v>
+        <v>0.009320274376450149</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00467588909313558</v>
+        <v>0.00935177818627116</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00469158558942943</v>
+        <v>0.009383171178858859</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004707226804572119</v>
+        <v>0.009414453609144238</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004722812865776137</v>
+        <v>0.009445625731552275</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004738343900001427</v>
+        <v>0.009476687800002853</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004753820033955858</v>
+        <v>0.009507640067911716</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004450261780104711</v>
+        <v>0.008900523560209423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004466745712362157</v>
+        <v>0.008933491424724315</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004483172555714586</v>
+        <v>0.008966345111429172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004499542440959323</v>
+        <v>0.008999084881918647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004515855498634556</v>
+        <v>0.009031710997269113</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004532111859019811</v>
+        <v>0.009064223718039622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004548311652136438</v>
+        <v>0.009096623304272876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004564455007748076</v>
+        <v>0.009128910015496152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004580542055361132</v>
+        <v>0.009161084110722265</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00459657292422525</v>
+        <v>0.009193145848450501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004612547743333789</v>
+        <v>0.009225095486667579</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004628466641424292</v>
+        <v>0.009256933282848583</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004644329746978948</v>
+        <v>0.009288659493957897</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004660137188225074</v>
+        <v>0.009320274376450149</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00467588909313558</v>
+        <v>0.00935177818627116</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00469158558942943</v>
+        <v>0.009383171178858859</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004707226804572119</v>
+        <v>0.009414453609144238</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004722812865776137</v>
+        <v>0.009445625731552275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004738343900001427</v>
+        <v>0.009476687800002853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004753820033955858</v>
+        <v>0.009507640067911716</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/79.xlsx
+++ b/BVSimulationFiles/79.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008900523560209423</v>
+        <v>0.08900523560209422</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008933491424724315</v>
+        <v>0.08933491424724314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008966345111429172</v>
+        <v>0.08966345111429172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008999084881918647</v>
+        <v>0.08999084881918647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009031710997269113</v>
+        <v>0.09031710997269113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009064223718039622</v>
+        <v>0.09064223718039623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009096623304272876</v>
+        <v>0.09096623304272876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009128910015496152</v>
+        <v>0.09128910015496151</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009161084110722265</v>
+        <v>0.09161084110722265</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009193145848450501</v>
+        <v>0.09193145848450501</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009225095486667579</v>
+        <v>0.09225095486667578</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009256933282848583</v>
+        <v>0.09256933282848584</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009288659493957897</v>
+        <v>0.09288659493957896</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009320274376450149</v>
+        <v>0.09320274376450149</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00935177818627116</v>
+        <v>0.09351778186271159</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009383171178858859</v>
+        <v>0.0938317117885886</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009414453609144238</v>
+        <v>0.09414453609144238</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009445625731552275</v>
+        <v>0.09445625731552275</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009476687800002853</v>
+        <v>0.09476687800002853</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009507640067911716</v>
+        <v>0.09507640067911716</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008900523560209423</v>
+        <v>0.08900523560209422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008933491424724315</v>
+        <v>0.08933491424724314</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008966345111429172</v>
+        <v>0.08966345111429172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008999084881918647</v>
+        <v>0.08999084881918647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009031710997269113</v>
+        <v>0.09031710997269113</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009064223718039622</v>
+        <v>0.09064223718039623</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009096623304272876</v>
+        <v>0.09096623304272876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009128910015496152</v>
+        <v>0.09128910015496151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009161084110722265</v>
+        <v>0.09161084110722265</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009193145848450501</v>
+        <v>0.09193145848450501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009225095486667579</v>
+        <v>0.09225095486667578</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009256933282848583</v>
+        <v>0.09256933282848584</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009288659493957897</v>
+        <v>0.09288659493957896</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009320274376450149</v>
+        <v>0.09320274376450149</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00935177818627116</v>
+        <v>0.09351778186271159</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009383171178858859</v>
+        <v>0.0938317117885886</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009414453609144238</v>
+        <v>0.09414453609144238</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009445625731552275</v>
+        <v>0.09445625731552275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009476687800002853</v>
+        <v>0.09476687800002853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009507640067911716</v>
+        <v>0.09507640067911716</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/79.xlsx
+++ b/BVSimulationFiles/79.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.004063157894736841</v>
+        <v>0.002662068965517241</v>
       </c>
       <c r="D1" t="n">
-        <v>0.008126315789473683</v>
+        <v>0.005324137931034483</v>
       </c>
       <c r="E1" t="n">
-        <v>0.01218947368421053</v>
+        <v>0.007986206896551724</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01625263157894737</v>
+        <v>0.01064827586206897</v>
       </c>
       <c r="G1" t="n">
-        <v>0.02031578947368421</v>
+        <v>0.01331034482758621</v>
       </c>
       <c r="H1" t="n">
-        <v>0.02437894736842105</v>
+        <v>0.01597241379310345</v>
       </c>
       <c r="I1" t="n">
-        <v>0.02844210526315789</v>
+        <v>0.01863448275862069</v>
       </c>
       <c r="J1" t="n">
-        <v>0.03250526315789473</v>
+        <v>0.02129655172413793</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03656842105263158</v>
+        <v>0.02395862068965517</v>
       </c>
       <c r="L1" t="n">
-        <v>0.04063157894736841</v>
+        <v>0.02662068965517241</v>
       </c>
       <c r="M1" t="n">
-        <v>0.04469473684210526</v>
+        <v>0.02928275862068966</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0487578947368421</v>
+        <v>0.0319448275862069</v>
       </c>
       <c r="O1" t="n">
-        <v>0.05282105263157894</v>
+        <v>0.03460689655172414</v>
       </c>
       <c r="P1" t="n">
-        <v>0.05688421052631579</v>
+        <v>0.03726896551724138</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.06094736842105263</v>
+        <v>0.03993103448275862</v>
       </c>
       <c r="R1" t="n">
-        <v>0.06501052631578946</v>
+        <v>0.04259310344827586</v>
       </c>
       <c r="S1" t="n">
-        <v>0.06907368421052631</v>
+        <v>0.0452551724137931</v>
       </c>
       <c r="T1" t="n">
-        <v>0.07313684210526315</v>
+        <v>0.04791724137931034</v>
       </c>
       <c r="U1" t="n">
+        <v>0.05057931034482759</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.05324137931034482</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.05590344827586206</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.05856551724137932</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.06122758620689656</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.0638896551724138</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.06655172413793103</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.06921379310344827</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.07187586206896551</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.07453793103448275</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.07719999999999999</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08900523560209422</v>
+        <v>0.2472185550982904</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08933491424724314</v>
+        <v>0.2475836246495546</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08966345111429172</v>
+        <v>0.2479464185832892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08999084881918647</v>
+        <v>0.2483069442211538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09031710997269113</v>
+        <v>0.2486652088652157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09064223718039623</v>
+        <v>0.2490212197979974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09096623304272876</v>
+        <v>0.249374984282525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09128910015496151</v>
+        <v>0.2497265095623755</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09161084110722265</v>
+        <v>0.2500758028617246</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09193145848450501</v>
+        <v>0.2504228713853942</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09225095486667578</v>
+        <v>0.2507677223189003</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09256933282848584</v>
+        <v>0.2511103628284996</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09288659493957896</v>
+        <v>0.2514508000612372</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09320274376450149</v>
+        <v>0.2517890411449935</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09351778186271159</v>
+        <v>0.2521250931885313</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0938317117885886</v>
+        <v>0.2524589632815428</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09414453609144238</v>
+        <v>0.252790658494696</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09445625731552275</v>
+        <v>0.2531201858796818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09476687800002853</v>
+        <v>0.2534475524692603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09507640067911716</v>
+        <v>0.2537727652773071</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2540958312988603</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.2544167575101661</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.254735550868725</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.255052218313338</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.255366766764153</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2556792031227088</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.2559895342719836</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.256297767076438</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.256603908382062</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2569079650164198</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08900523560209422</v>
+        <v>0.2472185550982904</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08933491424724314</v>
+        <v>0.2475836246495546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08966345111429172</v>
+        <v>0.2479464185832892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08999084881918647</v>
+        <v>0.2483069442211538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09031710997269113</v>
+        <v>0.2486652088652157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09064223718039623</v>
+        <v>0.2490212197979974</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09096623304272876</v>
+        <v>0.249374984282525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09128910015496151</v>
+        <v>0.2497265095623755</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09161084110722265</v>
+        <v>0.2500758028617246</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09193145848450501</v>
+        <v>0.2504228713853942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09225095486667578</v>
+        <v>0.2507677223189003</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09256933282848584</v>
+        <v>0.2511103628284996</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09288659493957896</v>
+        <v>0.2514508000612372</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09320274376450149</v>
+        <v>0.2517890411449935</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09351778186271159</v>
+        <v>0.2521250931885313</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0938317117885886</v>
+        <v>0.2524589632815428</v>
       </c>
       <c r="R3" t="n">
-        <v>0.09414453609144238</v>
+        <v>0.252790658494696</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09445625731552275</v>
+        <v>0.2531201858796818</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09476687800002853</v>
+        <v>0.2534475524692603</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09507640067911716</v>
+        <v>0.2537727652773071</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2540958312988603</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2544167575101661</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.254735550868725</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.255052218313338</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.255366766764153</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2556792031227088</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2559895342719836</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.256297767076438</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.256603908382062</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2569079650164198</v>
       </c>
     </row>
   </sheetData>
